--- a/demo_output/test/prompt_14/figure_06_10-årig amerikansk statsrente.xlsx
+++ b/demo_output/test/prompt_14/figure_06_10-årig amerikansk statsrente.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,217 +489,217 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.46</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.54</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.61</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.55</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.51</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.41</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.29</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.28</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.43</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4.47</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4.31</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4.24</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.22</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4.25</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4.23</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -709,7 +709,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -719,67 +719,67 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4.36</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4.48</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4.43</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>4.28</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -789,1737 +789,1737 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>4.18</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>4.23</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>4.17</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4.16</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>4.25</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>4.26</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>4.25</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4.28</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4.27</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>4.2</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4.15</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4.09</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>3.99</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>3.8</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>3.78</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>3.9</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>3.96</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>3.99</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>3.94</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>3.9</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>3.85</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>3.83</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>3.92</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>3.89</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>3.86</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>3.82</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>3.79</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>3.86</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>3.81</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>3.82</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>3.83</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>3.84</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>3.87</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>3.91</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>3.77</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>3.73</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>3.72</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>3.7</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>3.65</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>3.68</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>3.63</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>3.65</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>3.73</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>3.73</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>3.74</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>3.79</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>3.79</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>3.75</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>3.81</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>3.74</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>3.79</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>3.85</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>3.98</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>4.03</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>4.04</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>4.06</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>4.09</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>4.08</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>4.02</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>4.08</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>4.19</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>4.37</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>4.26</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>4.42</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>4.31</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>4.3</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>4.43</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>4.44</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>4.43</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>4.43</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>4.42</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>4.39</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>4.41</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>4.43</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>4.41</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>4.3</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>4.39</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>4.5</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>4.57</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>4.52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>4.59</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>4.59</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>4.58</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>4.62</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>4.55</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>4.58</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>4.57</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>4.6</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>4.62</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>4.67</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>4.67</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>4.68</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>4.77</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>4.79</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>4.78</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>4.66</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>4.61</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>4.61</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>4.57</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>4.6</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>4.65</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>4.63</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>4.53</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>4.55</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>4.55</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>4.52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>4.58</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>4.54</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>4.52</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>4.43</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>4.45</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>4.49</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>4.51</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>4.54</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>4.62</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>4.52</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>4.47</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>4.55</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>4.53</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>4.42</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>4.4</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>4.3</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>4.29</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>4.24</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>4.28</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4.32</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>4.28</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4.32</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>4.27</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>4.31</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>4.31</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>4.29</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>4.25</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -2529,647 +2529,647 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4.34</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>4.17</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>4.06</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>4.34</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>4.4</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>4.48</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>4.38</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>4.35</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>4.29</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>4.42</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>4.41</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>4.4</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>4.32</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>4.29</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>4.23</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>4.19</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>4.17</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>4.33</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>4.36</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>4.3</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>4.37</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>4.37</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>4.45</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>4.49</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>4.53</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>4.45</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>4.46</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>4.48</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>4.58</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>4.54</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>4.47</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>4.46</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>4.46</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>4.51</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>4.49</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>4.41</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
-        <v>4.41</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>4.46</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>4.38</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B269" s="2" t="n">
-        <v>4.34</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
@@ -3179,147 +3179,147 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>4.26</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>4.24</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>4.26</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>4.34</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
@@ -3329,2130 +3329,70 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>4.38</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>4.43</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="B293" s="2" t="n">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="B294" s="2" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="B295" s="2" t="n">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="1" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="B296" s="2" t="n">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B297" s="2" t="n">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="B298" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="n">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="n">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="n">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="n">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="B306" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="B307" s="2" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="B309" s="2" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="B310" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="B311" s="2" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="B312" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="B313" s="2" t="n">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="B314" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="B315" s="2" t="n">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="1" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="B317" s="2" t="n">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="B318" s="2" t="n">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="B319" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="B320" s="2" t="n">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="B321" s="2" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="B322" s="2" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="B323" s="2" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="B324" s="2" t="n">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="B325" s="2" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="B326" s="2" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="B327" s="2" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="B328" s="2" t="n">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="B329" s="2" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="B330" s="2" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="B331" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="B332" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="B333" s="2" t="n">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="B334" s="2" t="n">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="B335" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="B337" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="B338" s="2" t="n">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="B339" s="2" t="n">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="B340" s="2" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="B341" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="B342" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="B343" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="B344" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="B345" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="B346" s="2" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="B347" s="2" t="n">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="B348" s="2" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="B349" s="2" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="B350" s="2" t="n">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-20</t>
-        </is>
-      </c>
-      <c r="B351" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="B352" s="2" t="n">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="B353" s="2" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="B354" s="2" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="B355" s="2" t="n">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="B356" s="2" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="B357" s="2" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="B358" s="2" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="B359" s="2" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="B360" s="2" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="B361" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="B362" s="2" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="B363" s="2" t="n">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="B364" s="2" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="B365" s="2" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="B366" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="B367" s="2" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="B368" s="2" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="B369" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="B370" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="B371" s="2" t="n">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="B372" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="B373" s="2" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="B374" s="2" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="B375" s="2" t="n">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="B376" s="2" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="B377" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="B378" s="2" t="n">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="B379" s="2" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="B380" s="2" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="B381" s="2" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="B382" s="2" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="B383" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="B384" s="2" t="n">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="B385" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="B386" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="B387" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="B388" s="2" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="B389" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B390" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="B391" s="2" t="n">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="B392" s="2" t="n">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="B393" s="2" t="n">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="B394" s="2" t="n">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="B395" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="B396" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="B397" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="B398" s="2" t="n">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B399" s="2" t="n">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="1" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B400" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B401" s="2" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B402" s="2" t="n">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="B403" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="B404" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B405" s="2" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="B406" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="B407" s="2" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="B408" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="B409" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="B410" s="2" t="n">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="B411" s="2" t="n">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="B412" s="2" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="B413" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B414" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B415" s="2" t="n">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="B416" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="B417" s="2" t="n">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="B418" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="B419" s="2" t="n">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B420" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B421" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B422" s="2" t="n">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B423" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B424" s="2" t="n">
-        <v>4.21</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B425" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B426" s="2" t="n">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B427" s="2" t="n">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B428" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B429" s="2" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B430" s="2" t="n">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B431" s="2" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B432" s="2" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B433" s="2" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B434" s="2" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B435" s="2" t="n">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B436" s="2" t="n">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B437" s="2" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B438" s="2" t="n">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B439" s="2" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B440" s="2" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B441" s="2" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="B442" s="2" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="B443" s="2" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="B444" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B445" s="2" t="n">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B446" s="2" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B447" s="2" t="n">
-        <v>4.21</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="B448" s="2" t="n">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="B449" s="2" t="n">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B450" s="2" t="n">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="B451" s="2" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B452" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="B453" s="2" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B454" s="2" t="n">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="B455" s="2" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="B456" s="2" t="n">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="B457" s="2" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="B458" s="2" t="n">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="B459" s="2" t="n">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="B460" s="2" t="n">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="B461" s="2" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B462" s="2" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="B463" s="2" t="n">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="B464" s="2" t="n">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="B465" s="2" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="B466" s="2" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="B467" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B468" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B469" s="2" t="n">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B470" s="2" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="B471" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B472" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="B473" s="2" t="n">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="B474" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B475" s="2" t="n">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="B476" s="2" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="B477" s="2" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="B478" s="2" t="n">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B479" s="2" t="n">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B480" s="2" t="n">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B481" s="2" t="n">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="B482" s="2" t="n">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B483" s="2" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B484" s="2" t="n">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B485" s="2" t="n">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B486" s="2" t="n">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B487" s="2" t="n">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B488" s="2" t="n">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B489" s="2" t="n">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B490" s="2" t="n">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B491" s="2" t="n">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B492" s="2" t="n">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B493" s="2" t="n">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B494" s="2" t="n">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="B495" s="2" t="n">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="B496" s="2" t="n">
-        <v>4.67</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="B497" s="2" t="n">
-        <v>4.57</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B498" s="2" t="n">
         <v>4.57</v>
       </c>
     </row>
